--- a/data/trans_orig/P16A07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A07-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15220</t>
+          <t>15954</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489314</t>
+          <t>489221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>452269</t>
+          <t>451535</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>463559</t>
+          <t>462940</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>944724</t>
+          <t>944497</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>956890</t>
+          <t>956857</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15865</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30173</t>
+          <t>30178</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19018</t>
+          <t>18956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41014</t>
+          <t>40270</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>719624</t>
+          <t>719392</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>731424</t>
+          <t>731491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>595321</t>
+          <t>595316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>613456</t>
+          <t>614040</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1319968</t>
+          <t>1320712</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1341964</t>
+          <t>1342026</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>7912</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22521</t>
+          <t>23648</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>16834</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38338</t>
+          <t>36937</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28203</t>
+          <t>28700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53269</t>
+          <t>53312</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>615128</t>
+          <t>614001</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>630132</t>
+          <t>629737</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>651406</t>
+          <t>652807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>672673</t>
+          <t>672910</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1274125</t>
+          <t>1274082</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1299191</t>
+          <t>1298694</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20229</t>
+          <t>21137</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34231</t>
+          <t>33510</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59200</t>
+          <t>60117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43766</t>
+          <t>43595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73417</t>
+          <t>73104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>498918</t>
+          <t>498010</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>513090</t>
+          <t>513114</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>456442</t>
+          <t>455525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>481411</t>
+          <t>482132</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>961372</t>
+          <t>961685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>991023</t>
+          <t>991194</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>22481</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38718</t>
+          <t>38310</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65704</t>
+          <t>65623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50909</t>
+          <t>50759</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80847</t>
+          <t>80642</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>365133</t>
+          <t>364229</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>378473</t>
+          <t>378268</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>338282</t>
+          <t>338363</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>365268</t>
+          <t>365676</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>709849</t>
+          <t>710054</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>739787</t>
+          <t>739937</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19659</t>
+          <t>19291</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25121</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46552</t>
+          <t>46639</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33846</t>
+          <t>35277</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59622</t>
+          <t>59367</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>272924</t>
+          <t>273292</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286272</t>
+          <t>286413</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>296382</t>
+          <t>296295</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>317813</t>
+          <t>317612</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>575895</t>
+          <t>576150</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>601671</t>
+          <t>600240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,45%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>17812</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22145</t>
+          <t>22483</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45229</t>
+          <t>44457</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30386</t>
+          <t>30817</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56535</t>
+          <t>56944</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>192015</t>
+          <t>192071</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>204623</t>
+          <t>204964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>288679</t>
+          <t>289451</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>311763</t>
+          <t>311425</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>487256</t>
+          <t>486847</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>513405</t>
+          <t>512974</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55089</t>
+          <t>55132</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85755</t>
+          <t>88484</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>190280</t>
+          <t>190996</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>246748</t>
+          <t>247695</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>255230</t>
+          <t>259067</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>320257</t>
+          <t>319516</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3189770</t>
+          <t>3187041</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3220436</t>
+          <t>3220393</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3132449</t>
+          <t>3131502</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3188917</t>
+          <t>3188201</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6334465</t>
+          <t>6335206</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6399492</t>
+          <t>6395655</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>817</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12504</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>445963</t>
+          <t>445007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452305</t>
+          <t>452288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>420197</t>
+          <t>420276</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427427</t>
+          <t>427432</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>869007</t>
+          <t>869970</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>879268</t>
+          <t>879521</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>20514</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11684</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31722</t>
+          <t>30667</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43718</t>
+          <t>43582</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>665746</t>
+          <t>665724</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>681234</t>
+          <t>680590</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>577492</t>
+          <t>578547</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>597530</t>
+          <t>597547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1251733</t>
+          <t>1251869</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1275213</t>
+          <t>1275303</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>12656</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33916</t>
+          <t>33961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42890</t>
+          <t>42730</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72600</t>
+          <t>72647</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61039</t>
+          <t>61708</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97894</t>
+          <t>97011</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>646138</t>
+          <t>646093</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667072</t>
+          <t>667398</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>635054</t>
+          <t>635007</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>664764</t>
+          <t>664924</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1289814</t>
+          <t>1290697</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1326669</t>
+          <t>1326000</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12456</t>
+          <t>12935</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33762</t>
+          <t>32740</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44581</t>
+          <t>43726</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>71760</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60680</t>
+          <t>62721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95855</t>
+          <t>97290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>580855</t>
+          <t>581877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>602161</t>
+          <t>601682</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>540636</t>
+          <t>542312</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>569491</t>
+          <t>570346</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1132834</t>
+          <t>1131399</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1168009</t>
+          <t>1165968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>16060</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36044</t>
+          <t>37005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56105</t>
+          <t>55633</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87543</t>
+          <t>86537</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77580</t>
+          <t>77941</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116304</t>
+          <t>115074</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>391258</t>
+          <t>390297</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>411639</t>
+          <t>411242</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>360257</t>
+          <t>361263</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>391695</t>
+          <t>392167</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>758798</t>
+          <t>760028</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>797522</t>
+          <t>797161</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,09%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22700</t>
+          <t>23291</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33315</t>
+          <t>35144</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59457</t>
+          <t>60539</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46152</t>
+          <t>46292</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74412</t>
+          <t>75069</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285095</t>
+          <t>284504</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>300593</t>
+          <t>300737</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>294539</t>
+          <t>293457</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>320681</t>
+          <t>318852</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>587379</t>
+          <t>586722</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>615639</t>
+          <t>615499</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24260</t>
+          <t>23963</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32731</t>
+          <t>32709</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59224</t>
+          <t>59077</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44342</t>
+          <t>42334</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73517</t>
+          <t>73746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>224776</t>
+          <t>225073</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241428</t>
+          <t>241487</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>326449</t>
+          <t>326596</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>352942</t>
+          <t>352964</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>561192</t>
+          <t>560963</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>590367</t>
+          <t>592375</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>86572</t>
+          <t>86537</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133555</t>
+          <t>132995</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>262752</t>
+          <t>264554</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>328478</t>
+          <t>331394</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>367529</t>
+          <t>364473</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>448340</t>
+          <t>448511</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3284592</t>
+          <t>3285152</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3331575</t>
+          <t>3331610</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3218337</t>
+          <t>3215421</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3284063</t>
+          <t>3282261</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6516621</t>
+          <t>6516450</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6597432</t>
+          <t>6600488</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9058</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>921</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>10914</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410405</t>
+          <t>412486</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>388029</t>
+          <t>388008</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394831</t>
+          <t>394834</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>804248</t>
+          <t>804304</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>813319</t>
+          <t>813265</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20139</t>
+          <t>21198</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10412</t>
+          <t>11410</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26644</t>
+          <t>27196</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>578658</t>
+          <t>577719</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>588524</t>
+          <t>588384</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>543405</t>
+          <t>542346</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>556903</t>
+          <t>556821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1127396</t>
+          <t>1126844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1143628</t>
+          <t>1142630</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23007</t>
+          <t>23439</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19063</t>
+          <t>19737</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38496</t>
+          <t>40516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30671</t>
+          <t>30759</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55368</t>
+          <t>54923</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>646090</t>
+          <t>645658</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661421</t>
+          <t>661453</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>622890</t>
+          <t>620870</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>642323</t>
+          <t>641649</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1275115</t>
+          <t>1275560</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1299812</t>
+          <t>1299724</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>9169</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26646</t>
+          <t>24376</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42357</t>
+          <t>42046</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72393</t>
+          <t>71685</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56453</t>
+          <t>56217</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89570</t>
+          <t>92234</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>619402</t>
+          <t>621672</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>636682</t>
+          <t>636879</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>576684</t>
+          <t>577392</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>606720</t>
+          <t>607031</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1205555</t>
+          <t>1202891</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1238672</t>
+          <t>1238908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30152</t>
+          <t>30992</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43092</t>
+          <t>42371</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71079</t>
+          <t>71836</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58809</t>
+          <t>58969</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93007</t>
+          <t>93059</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>447766</t>
+          <t>446926</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>466400</t>
+          <t>466166</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>425770</t>
+          <t>425013</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>453757</t>
+          <t>454478</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>881760</t>
+          <t>881708</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>915958</t>
+          <t>915798</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13440</t>
+          <t>12590</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39406</t>
+          <t>38055</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67226</t>
+          <t>64677</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44478</t>
+          <t>42666</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75603</t>
+          <t>73513</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>320890</t>
+          <t>321740</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>331438</t>
+          <t>331523</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>310536</t>
+          <t>313085</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>338356</t>
+          <t>339707</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>636489</t>
+          <t>638579</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>667614</t>
+          <t>669426</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>17071</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33983</t>
+          <t>32631</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63094</t>
+          <t>62401</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43941</t>
+          <t>43633</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73856</t>
+          <t>75394</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>239265</t>
+          <t>239927</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>251247</t>
+          <t>251083</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>337075</t>
+          <t>337768</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>366186</t>
+          <t>367538</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>583311</t>
+          <t>581773</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>613226</t>
+          <t>613534</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57849</t>
+          <t>58629</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>91412</t>
+          <t>92928</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>223043</t>
+          <t>220920</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>283410</t>
+          <t>288598</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>290464</t>
+          <t>294186</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>362774</t>
+          <t>365908</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3302938</t>
+          <t>3301422</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3336501</t>
+          <t>3335721</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3261132</t>
+          <t>3255944</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3321499</t>
+          <t>3323622</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6576118</t>
+          <t>6572984</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6648428</t>
+          <t>6644706</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2213</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18695</t>
+          <t>19671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21866</t>
+          <t>19439</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>392903</t>
+          <t>391181</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294505</t>
+          <t>293529</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311000</t>
+          <t>310987</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>691321</t>
+          <t>693748</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>709767</t>
+          <t>710483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23469</t>
+          <t>23922</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28096</t>
+          <t>27339</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>416361</t>
+          <t>415630</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423383</t>
+          <t>423381</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>488035</t>
+          <t>487582</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505315</t>
+          <t>504828</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>906955</t>
+          <t>907712</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>925893</t>
+          <t>925984</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7661</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>24636</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>17400</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32894</t>
+          <t>32531</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>28752</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51213</t>
+          <t>52204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>513038</t>
+          <t>511702</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>528677</t>
+          <t>528382</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>509574</t>
+          <t>509937</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>524476</t>
+          <t>525068</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1027593</t>
+          <t>1026602</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1050544</t>
+          <t>1050054</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15211</t>
+          <t>13254</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56184</t>
+          <t>54075</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44669</t>
+          <t>44339</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69784</t>
+          <t>68760</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52547</t>
+          <t>57447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116351</t>
+          <t>117366</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>831602</t>
+          <t>833711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>872575</t>
+          <t>874532</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>643097</t>
+          <t>644121</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>668212</t>
+          <t>668542</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1484316</t>
+          <t>1483301</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1548120</t>
+          <t>1543220</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23247</t>
+          <t>23639</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46383</t>
+          <t>45124</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57524</t>
+          <t>58142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80821</t>
+          <t>81772</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87618</t>
+          <t>87173</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118457</t>
+          <t>119936</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>513854</t>
+          <t>515113</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>536990</t>
+          <t>536598</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>464066</t>
+          <t>463115</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>487363</t>
+          <t>486745</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>986667</t>
+          <t>985188</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1017506</t>
+          <t>1017951</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14449</t>
+          <t>14766</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19202</t>
+          <t>19311</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77952</t>
+          <t>77228</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>29082</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78388</t>
+          <t>77377</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>353716</t>
+          <t>353399</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>363117</t>
+          <t>363282</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>530416</t>
+          <t>531140</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>589166</t>
+          <t>589057</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>898145</t>
+          <t>899156</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>946875</t>
+          <t>947451</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>12250</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>24792</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34681</t>
+          <t>34739</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52575</t>
+          <t>52070</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50024</t>
+          <t>49787</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71581</t>
+          <t>71202</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>257331</t>
+          <t>257477</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>270495</t>
+          <t>270019</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>371819</t>
+          <t>372324</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>389713</t>
+          <t>389655</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>635082</t>
+          <t>635461</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>656639</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84745</t>
+          <t>85505</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>135474</t>
+          <t>134337</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>210501</t>
+          <t>214142</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>291456</t>
+          <t>293572</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>322144</t>
+          <t>323773</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>414280</t>
+          <t>413007</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3322856</t>
+          <t>3323993</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3373585</t>
+          <t>3372825</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3366246</t>
+          <t>3364130</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3447201</t>
+          <t>3443560</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6701752</t>
+          <t>6703025</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6793888</t>
+          <t>6792259</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A07-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A07-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,69 +753,69 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8490</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3913</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15957</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>9442</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>4679</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>17982</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8490</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4549</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15954</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>9442</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>4696</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>17056</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489221</t>
+          <t>488267</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,77 +861,77 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>458999</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>451532</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>463576</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,59%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>952111</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>943571</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>956874</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>99,02%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>458999</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>451535</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>462940</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>978</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>952111</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>944497</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>956857</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16097</t>
+          <t>15941</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>12127</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30178</t>
+          <t>30771</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40270</t>
+          <t>40255</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>719392</t>
+          <t>719548</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>731491</t>
+          <t>731126</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>595316</t>
+          <t>594723</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>614040</t>
+          <t>613367</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1320712</t>
+          <t>1320727</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23648</t>
+          <t>23315</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>16377</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36937</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28700</t>
+          <t>27891</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53312</t>
+          <t>53628</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614001</t>
+          <t>614334</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>629737</t>
+          <t>629967</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>652807</t>
+          <t>653524</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>672910</t>
+          <t>673367</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1274082</t>
+          <t>1273766</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1298694</t>
+          <t>1299503</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>19962</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33510</t>
+          <t>34729</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60117</t>
+          <t>59469</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43595</t>
+          <t>44493</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73104</t>
+          <t>73853</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>498010</t>
+          <t>499185</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>513114</t>
+          <t>513270</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>455525</t>
+          <t>456173</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>482132</t>
+          <t>480913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>961685</t>
+          <t>960936</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>991194</t>
+          <t>990296</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22481</t>
+          <t>23121</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38310</t>
+          <t>38058</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65623</t>
+          <t>64865</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50759</t>
+          <t>50602</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80642</t>
+          <t>81082</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364229</t>
+          <t>363589</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>378268</t>
+          <t>378547</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>338363</t>
+          <t>339121</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>365676</t>
+          <t>365928</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>710054</t>
+          <t>709614</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>739937</t>
+          <t>740094</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,6%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19291</t>
+          <t>18803</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>25152</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46639</t>
+          <t>46830</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35277</t>
+          <t>34156</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59367</t>
+          <t>58844</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>273292</t>
+          <t>273780</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286413</t>
+          <t>286826</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>296295</t>
+          <t>296104</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>317612</t>
+          <t>317782</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>576150</t>
+          <t>576673</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>600240</t>
+          <t>601361</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17812</t>
+          <t>18074</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22483</t>
+          <t>23048</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44457</t>
+          <t>46258</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30817</t>
+          <t>31091</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56944</t>
+          <t>58518</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>192071</t>
+          <t>191809</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>204964</t>
+          <t>204622</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>289451</t>
+          <t>287650</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>311425</t>
+          <t>310860</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>486847</t>
+          <t>485273</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>512974</t>
+          <t>512700</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55132</t>
+          <t>54910</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>88484</t>
+          <t>87621</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>190996</t>
+          <t>190667</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>247695</t>
+          <t>247809</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>259067</t>
+          <t>256746</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>319516</t>
+          <t>323336</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3187041</t>
+          <t>3187904</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3220393</t>
+          <t>3220615</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3131502</t>
+          <t>3131388</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3188201</t>
+          <t>3188530</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6335206</t>
+          <t>6331386</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6395655</t>
+          <t>6397976</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>810</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>12276</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>445007</t>
+          <t>445370</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452288</t>
+          <t>452295</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427432</t>
+          <t>427428</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>869970</t>
+          <t>869235</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>879521</t>
+          <t>879528</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20514</t>
+          <t>19645</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>11150</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30667</t>
+          <t>29713</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>19977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43582</t>
+          <t>43259</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>665724</t>
+          <t>666593</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>680590</t>
+          <t>681411</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>578547</t>
+          <t>579501</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>597547</t>
+          <t>598064</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1251869</t>
+          <t>1252192</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1275303</t>
+          <t>1275474</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>13295</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33961</t>
+          <t>35272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42730</t>
+          <t>42640</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72647</t>
+          <t>73317</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61708</t>
+          <t>60143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97011</t>
+          <t>97300</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>646093</t>
+          <t>644782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667398</t>
+          <t>666759</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>635007</t>
+          <t>634337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>664924</t>
+          <t>665014</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1290697</t>
+          <t>1290408</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1326000</t>
+          <t>1327565</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>12626</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32740</t>
+          <t>32964</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43726</t>
+          <t>44210</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71760</t>
+          <t>71770</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62721</t>
+          <t>62316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97290</t>
+          <t>96075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>581877</t>
+          <t>581653</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>601682</t>
+          <t>601991</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>542312</t>
+          <t>542302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>570346</t>
+          <t>569862</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1131399</t>
+          <t>1132614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1165968</t>
+          <t>1166373</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16060</t>
+          <t>16482</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37005</t>
+          <t>36929</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55633</t>
+          <t>57307</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>86537</t>
+          <t>88028</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77941</t>
+          <t>78263</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115074</t>
+          <t>116507</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>390297</t>
+          <t>390373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>411242</t>
+          <t>410820</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>361263</t>
+          <t>359772</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>392167</t>
+          <t>390493</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>760028</t>
+          <t>758595</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>797161</t>
+          <t>796839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23291</t>
+          <t>22991</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35144</t>
+          <t>34398</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60539</t>
+          <t>58880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46292</t>
+          <t>46217</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75069</t>
+          <t>76002</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284504</t>
+          <t>284804</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>300737</t>
+          <t>300631</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>293457</t>
+          <t>295116</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>318852</t>
+          <t>319598</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>586722</t>
+          <t>585789</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>615499</t>
+          <t>615574</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,02%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23963</t>
+          <t>23488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32709</t>
+          <t>32192</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59077</t>
+          <t>57881</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42334</t>
+          <t>43528</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73746</t>
+          <t>73448</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225073</t>
+          <t>225548</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241487</t>
+          <t>241587</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>326596</t>
+          <t>327792</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>352964</t>
+          <t>353481</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>560963</t>
+          <t>561261</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>592375</t>
+          <t>591181</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>86537</t>
+          <t>86262</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>132995</t>
+          <t>133819</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>264554</t>
+          <t>262954</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>331394</t>
+          <t>334706</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>364473</t>
+          <t>362663</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>448511</t>
+          <t>444459</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3285152</t>
+          <t>3284328</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3331610</t>
+          <t>3331885</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3215421</t>
+          <t>3212109</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3282261</t>
+          <t>3283861</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6516450</t>
+          <t>6520502</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6600488</t>
+          <t>6602298</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7747</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10914</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412486</t>
+          <t>411815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>388008</t>
+          <t>388040</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>394834</t>
+          <t>394830</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>804304</t>
+          <t>804267</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>813265</t>
+          <t>813311</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12777</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6723</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21198</t>
+          <t>19456</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>10573</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27196</t>
+          <t>27240</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>577719</t>
+          <t>578480</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>588384</t>
+          <t>587638</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>542346</t>
+          <t>544088</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>556821</t>
+          <t>556917</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1126844</t>
+          <t>1126800</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1142630</t>
+          <t>1143467</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23439</t>
+          <t>22502</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19737</t>
+          <t>19470</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40516</t>
+          <t>39410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30759</t>
+          <t>31141</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54923</t>
+          <t>56101</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>645658</t>
+          <t>646595</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661453</t>
+          <t>660760</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>620870</t>
+          <t>621976</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>641649</t>
+          <t>641916</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1275560</t>
+          <t>1274382</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1299724</t>
+          <t>1299342</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24376</t>
+          <t>25343</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42046</t>
+          <t>41604</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71685</t>
+          <t>70692</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56217</t>
+          <t>56097</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92234</t>
+          <t>89118</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>621672</t>
+          <t>620705</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>636879</t>
+          <t>636254</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>577392</t>
+          <t>578385</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>607031</t>
+          <t>607473</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1202891</t>
+          <t>1206007</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1238908</t>
+          <t>1239028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30992</t>
+          <t>30006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42371</t>
+          <t>42668</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71836</t>
+          <t>70766</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58969</t>
+          <t>58088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93059</t>
+          <t>92291</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>446926</t>
+          <t>447912</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>466166</t>
+          <t>466870</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>425013</t>
+          <t>426083</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>454478</t>
+          <t>454181</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>881708</t>
+          <t>882476</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>915798</t>
+          <t>916679</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12590</t>
+          <t>14516</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38055</t>
+          <t>39056</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64677</t>
+          <t>66311</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42666</t>
+          <t>43531</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73513</t>
+          <t>73477</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>321740</t>
+          <t>319814</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>331523</t>
+          <t>331447</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>313085</t>
+          <t>311451</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>339707</t>
+          <t>338706</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>638579</t>
+          <t>638615</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>669426</t>
+          <t>668561</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>16938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,82 +8764,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>47178</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>34670</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>63600</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>11,79%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>15,89%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>57451</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>43640</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>74189</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>6,64%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>47178</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>32631</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>62401</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>15,59%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>57451</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>43633</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>75394</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>239927</t>
+          <t>240060</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>251083</t>
+          <t>251515</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>337768</t>
+          <t>336569</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>367538</t>
+          <t>365499</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>581773</t>
+          <t>582978</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>613534</t>
+          <t>613527</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58629</t>
+          <t>58476</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92928</t>
+          <t>94031</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>220920</t>
+          <t>223117</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>288598</t>
+          <t>286399</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>294186</t>
+          <t>294586</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>365908</t>
+          <t>366535</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3301422</t>
+          <t>3300319</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3335721</t>
+          <t>3335874</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3255944</t>
+          <t>3258143</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3323622</t>
+          <t>3321425</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6572984</t>
+          <t>6572357</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6644706</t>
+          <t>6644306</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>10029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>7804</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19671</t>
+          <t>18356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19439</t>
+          <t>22570</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>398484</t>
+          <t>404832</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>391181</t>
+          <t>397764</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>305971</t>
+          <t>354708</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293529</t>
+          <t>344156</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310987</t>
+          <t>360315</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>704455</t>
+          <t>759540</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>693748</t>
+          <t>747735</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>710483</t>
+          <t>766009</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>10978</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13787</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23922</t>
+          <t>24759</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16074</t>
+          <t>17897</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9067</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>28957</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>421260</t>
+          <t>472839</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415630</t>
+          <t>465912</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423381</t>
+          <t>475714</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>497717</t>
+          <t>487237</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>487582</t>
+          <t>476324</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>504828</t>
+          <t>493410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>918977</t>
+          <t>960076</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>907712</t>
+          <t>949016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>925984</t>
+          <t>966982</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14218</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24636</t>
+          <t>26523</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24693</t>
+          <t>27638</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17400</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32531</t>
+          <t>36830</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>38911</t>
+          <t>42300</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28752</t>
+          <t>31489</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52204</t>
+          <t>55660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>522120</t>
+          <t>606175</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511702</t>
+          <t>594314</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>528382</t>
+          <t>612725</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>517775</t>
+          <t>594501</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>509937</t>
+          <t>585309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>525068</t>
+          <t>602662</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1039895</t>
+          <t>1200676</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1026602</t>
+          <t>1187316</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1050054</t>
+          <t>1211487</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34881</t>
+          <t>37388</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>26764</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54075</t>
+          <t>52955</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56444</t>
+          <t>61485</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44339</t>
+          <t>50857</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68760</t>
+          <t>73770</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>91324</t>
+          <t>98873</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57447</t>
+          <t>83427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117366</t>
+          <t>116909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>852905</t>
+          <t>663229</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>833711</t>
+          <t>647662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>874532</t>
+          <t>673853</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>656437</t>
+          <t>675401</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>644121</t>
+          <t>663116</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>668542</t>
+          <t>686029</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1509343</t>
+          <t>1338631</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1483301</t>
+          <t>1320595</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1543220</t>
+          <t>1354077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32795</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23639</t>
+          <t>24593</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>45973</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>69072</t>
+          <t>76553</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58142</t>
+          <t>64882</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81772</t>
+          <t>90726</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>101867</t>
+          <t>110848</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87173</t>
+          <t>94801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119936</t>
+          <t>129304</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>527442</t>
+          <t>574064</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>515113</t>
+          <t>562386</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>536598</t>
+          <t>583766</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>475815</t>
+          <t>530895</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>463115</t>
+          <t>516722</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>486745</t>
+          <t>542566</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1003257</t>
+          <t>1104959</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>985188</t>
+          <t>1086503</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1017951</t>
+          <t>1121006</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14766</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48197</t>
+          <t>52275</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>43198</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77228</t>
+          <t>63321</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>56975</t>
+          <t>61830</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29082</t>
+          <t>50938</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77377</t>
+          <t>74257</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>359387</t>
+          <t>397526</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>353399</t>
+          <t>391015</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>363282</t>
+          <t>401948</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>560171</t>
+          <t>386891</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>531140</t>
+          <t>375845</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>589057</t>
+          <t>395968</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>919558</t>
+          <t>784416</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>899156</t>
+          <t>771989</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>947451</t>
+          <t>795308</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>17294</t>
+          <t>18843</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12250</t>
+          <t>12469</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24792</t>
+          <t>26343</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,17 +11758,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>42775</t>
+          <t>46656</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34739</t>
+          <t>37525</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52070</t>
+          <t>56972</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>60069</t>
+          <t>65498</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49787</t>
+          <t>53189</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71202</t>
+          <t>78291</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>264975</t>
+          <t>290860</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>257477</t>
+          <t>283360</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>270019</t>
+          <t>297234</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>381619</t>
+          <t>416423</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>372324</t>
+          <t>406107</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>389655</t>
+          <t>425554</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>646594</t>
+          <t>707284</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>635461</t>
+          <t>694491</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>719593</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,12%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282269</t>
+          <t>309703</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424394</t>
+          <t>463079</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706663</t>
+          <t>772782</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>111757</t>
+          <t>121754</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85505</t>
+          <t>100742</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>134337</t>
+          <t>146123</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>262196</t>
+          <t>286257</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>214142</t>
+          <t>259442</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>293572</t>
+          <t>312595</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>373953</t>
+          <t>408011</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>323773</t>
+          <t>375286</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>413007</t>
+          <t>444858</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3346573</t>
+          <t>3409526</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3323993</t>
+          <t>3385157</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3372825</t>
+          <t>3430538</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3395506</t>
+          <t>3446056</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3364130</t>
+          <t>3419718</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3443560</t>
+          <t>3472871</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6742079</t>
+          <t>6855582</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6703025</t>
+          <t>6818735</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6792259</t>
+          <t>6888307</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3657702</t>
+          <t>3732313</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7116032</t>
+          <t>7263593</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
